--- a/modelling/model_manual_drops.xlsx
+++ b/modelling/model_manual_drops.xlsx
@@ -1,19 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susanacunha/Documents/PhD/iNat_analysis_clean/modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE681C6E-D7AD-C74B-A027-4F40B3183BCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{314B532D-6303-1F4A-A17C-B43EFBFD479E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{7C728923-D501-ED44-A77E-3B510BEF037C}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="14280" activeTab="3" xr2:uid="{7C728923-D501-ED44-A77E-3B510BEF037C}"/>
   </bookViews>
   <sheets>
     <sheet name="drops" sheetId="2" r:id="rId1"/>
+    <sheet name="table manual drops" sheetId="5" r:id="rId2"/>
+    <sheet name="table drop1s" sheetId="6" r:id="rId3"/>
+    <sheet name="table var bins" sheetId="8" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="94">
   <si>
     <t>AIC</t>
   </si>
@@ -126,16 +129,220 @@
   </si>
   <si>
     <t>Full model: fit_full &lt;- glmmTMB(rg ~ log_ysu + Nph + Nproj + Nobsf + Ntags + Nnotes +  n_info_no_proj:Nproj + n_info_no_obsf:Nobsf+ n_info_no_tags:Ntags + n_info_no_notes:Nnotes + (1|observed_on_month) +(1|species) + (1|genus),  data = data_30_test_month, family="binomial", na.action ="na.fail")</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>deltaAIC</t>
+  </si>
+  <si>
+    <t>Y + NPh + NPr + NO + NT + PN + NE:NPr + NE:NO + NE:NT + NE:PN + (1|M) + (1|S) + (1|G)</t>
+  </si>
+  <si>
+    <t>Y + NPh + PPr + NO + NT + LN + NE:PPr + NE:NO + NE:NT + NE:LN + (1|M) + (1|S) + (1|G)</t>
+  </si>
+  <si>
+    <t>Y + NPh + NPr + NO + NT + LN + NE:NPr + NE:NO + NE:NT + NE:LN + (1|M) + (1|S) + (1|G)</t>
+  </si>
+  <si>
+    <t>Y + NPh + NPr + NO + PT + LN + NE:NPr + NE:NO + NE:PT + NE:LN + (1|M) + (1|S) + (1|G)</t>
+  </si>
+  <si>
+    <t>Y + NPh + PPr + PO + NT + PN + NE:PPr + NE:PO + NE:NT + NE:PN + (1|M) + (1|S) + (1|G)</t>
+  </si>
+  <si>
+    <t>Y + NPh + PPr + PO + PT + PN + NE:PPr + NE:PO + NE:PT+ NE:PN + (1|M) + (1|S) + (1|G)</t>
+  </si>
+  <si>
+    <t>Y + NPh + NPr + PO + NT + PN + NE:NPr + NE:PO + NE:NT + NE:PN + (1|M) + (1|S) + (1|G)</t>
+  </si>
+  <si>
+    <t>Y + NPh + NPr + PO + PT + PN + NE:NPr + NE:PO + NE:PT + NE:PN + (1|M) + (1|S) + (1|G)</t>
+  </si>
+  <si>
+    <t>Y + NPh + PPr + PO + NT + LN + NE:PPr + NE:PO + NE:NT + NE:LN + (1|M) + (1|S) + (1|G)</t>
+  </si>
+  <si>
+    <t>Y + NPh + NPr + PO + NT + LN + NE:NPr + NE:PO + NE:NT + NE:LN + (1|M) + (1|S) + (1|G)</t>
+  </si>
+  <si>
+    <t>Y + NPh + NPr + PO + PT + LN + NE:NPr + NE:PO + NE:PT + NE:LN + (1|M) + (1|S) + (1|G)</t>
+  </si>
+  <si>
+    <t>NPh + PPr + PO + NT + PN + NE:PPr + NE:PO + NE:NT + NE:PN + (1|M) + (1|S) + (1|G)</t>
+  </si>
+  <si>
+    <t>Y + PPr + PO + NT + PN + NE:PPr + NE:PO + NE:NT + NE:PN + (1|M) + (1|S) + (1|G)</t>
+  </si>
+  <si>
+    <t>Y + NPh + PPr + PO + NT + PN + NE:PPr + NE:PO + NE:PN + (1|M) + (1|S) + (1|G)</t>
+  </si>
+  <si>
+    <t>Y + NPh + PPr + PO + NT + PN + NE:PO + NE:NT + NE:PN + (1|M) + (1|S) + (1|G)</t>
+  </si>
+  <si>
+    <t>Y + NPh + PPr + PO + NT + PN + NE:PPr + NE:NT + NE:PN + (1|M) + (1|S) + (1|G)</t>
+  </si>
+  <si>
+    <t>NPh + PPr + PO + NT + PN + NE:PPr + NE:PO + NE:PN + (1|M) + (1|S) + (1|G)</t>
+  </si>
+  <si>
+    <t>Y + PPr + PO + NT + PN + NE:PPr + NE:PO + NE:PN + (1|M) + (1|S) + (1|G)</t>
+  </si>
+  <si>
+    <t>Y + NPh + PPr + PO + PN + NE:PPr + NE:PO + NE:PN + (1|M) + (1|S) + (1|G)</t>
+  </si>
+  <si>
+    <t>Y + NPh + PPr + PO + NT + PN + NE:PPr + NE:PO + (1|M) + (1|S) + (1|G)</t>
+  </si>
+  <si>
+    <t>Y + NPh + PPr + PO + NT + PN + NE:PPr + NE:PN + (1|M) + (1|S) + (1|G)</t>
+  </si>
+  <si>
+    <t>Y + NPh + PPr + PO + NT + PN + NE:PO + NE:PN + (1|M) + (1|S) + (1|G)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                    labels=c("1","2","3","4","5-10", "&gt;10")),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                projects_binned = cut(n_projects, breaks = c(-Inf, 0,1,2,3,4,10,Inf), </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                      labels=c("0","1","2","3","4","5-10", "&gt;10")),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                obsf_binned = cut(n_obs_fields, breaks = c(-Inf, 0,1,2,3,4,10,Inf), </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                  labels=c("0","1","2","3","4","5-10", "&gt;10")),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                notes_binned = cut(length_notes, breaks = c(-Inf, 0, 25, 50,100, 300, Inf), </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                   labels=c("0", "1-25", "26-50", "51-100", "101-300", "&gt;300")),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                tags_binned = cut(n_tags, breaks = c(-Inf,0,1,2,5,10,30,Inf), </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                  labels=c("0","1","2","3-5","6-10","11-30", "&gt;30")),</t>
+  </si>
+  <si>
+    <t># quantile(df %&gt;% filter(length_notes&gt;0) %&gt;% pull(length_notes), c(0.5,0.75, 0.9, 0.95, 0.99,1))</t>
+  </si>
+  <si>
+    <t># ecdf(df %&gt;% filter(length_notes&gt;0) %&gt;% pull(length_notes)) (c(25, 50,100, 300, Inf))</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># # </t>
+  </si>
+  <si>
+    <t># quantile(df %&gt;% filter(n_tags&gt;1) %&gt;% pull(n_tags), c(0.5,0.75, 0.9, 0.95, 0.99,1))</t>
+  </si>
+  <si>
+    <t># ecdf(df %&gt;% filter(n_tags&gt;1) %&gt;% pull(n_tags)) (c(1,2,5,10,30,Inf))</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># </t>
+  </si>
+  <si>
+    <t># quantile(df %&gt;% filter(n_obs_fields&gt;1) %&gt;% pull(n_obs_fields), c(0.5,0.75, 0.9, 0.95, 0.99,1))</t>
+  </si>
+  <si>
+    <t># ecdf(df %&gt;% filter(n_obs_fields&gt;1) %&gt;% pull(n_obs_fields)) (c(1,2,3,4,10,Inf))</t>
+  </si>
+  <si>
+    <t># quantile(df %&gt;% filter(n_projects&gt;1) %&gt;% pull(n_projects), c(0.5,0.75, 0.9, 0.95, 0.99,1))</t>
+  </si>
+  <si>
+    <t># ecdf(df %&gt;% filter(n_projects&gt;1) %&gt;% pull(n_projects)) (c(1,2,3,4,10,Inf))</t>
+  </si>
+  <si>
+    <t># quantile(df %&gt;% pull(n_photos), c(0,0.5,0.75, 0.9, 0.95, 0.99,1))</t>
+  </si>
+  <si>
+    <t># ecdf(df %&gt;% pull(n_photos)) (c(1,2,3,4,10,Inf))</t>
+  </si>
+  <si>
+    <t>photos</t>
+  </si>
+  <si>
+    <t>photos_binned = cut(n_photos, breaks = c(0,1,2,3,4,10,Inf)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "&gt;10"</t>
+  </si>
+  <si>
+    <t>"5-10"</t>
+  </si>
+  <si>
+    <t>projects</t>
+  </si>
+  <si>
+    <t>obsf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "1-25"</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "26-50"</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "51-100"</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "101-300"</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "&gt;300"</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "&gt;10</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>tags</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "&gt;30"</t>
+  </si>
+  <si>
+    <t>"3-5"</t>
+  </si>
+  <si>
+    <t>"6-10"</t>
+  </si>
+  <si>
+    <t>"11-30"</t>
+  </si>
+  <si>
+    <t>TABLE:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -173,13 +380,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -954,7 +1168,7 @@
         <v>1458487</v>
       </c>
       <c r="D43">
-        <f t="shared" si="4"/>
+        <f>C43-$C$40</f>
         <v>278</v>
       </c>
     </row>
@@ -1001,6 +1215,678 @@
       <c r="D46">
         <f t="shared" si="4"/>
         <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BD832AD-86ED-7944-ADD2-322213DCF5C8}">
+  <dimension ref="A1:D34"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="81.5" customWidth="1"/>
+    <col min="3" max="3" width="15.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2">
+        <v>1458210</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3">
+        <v>1458312</v>
+      </c>
+      <c r="D3">
+        <f>C3-$C$2</f>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4">
+        <v>1458583</v>
+      </c>
+      <c r="D4">
+        <f t="shared" ref="D4:D12" si="0">C4-$C$2</f>
+        <v>373</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5">
+        <v>1458679</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>469</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6">
+        <v>1458850</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>640</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7">
+        <v>1459220</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8">
+        <v>1459323</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9">
+        <v>1459633</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10">
+        <v>1459784</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11">
+        <v>1460264</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12">
+        <v>1460331</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B25" s="7"/>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B27" s="7"/>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B31" s="7"/>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B32" s="7"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B33" s="7"/>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B34" s="7"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:C15">
+    <sortCondition ref="C2:C15"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE12680-0292-8749-A3E0-59E6D45F805A}">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="72.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2">
+        <v>1458209</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3">
+        <v>1458210</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ref="D3:D14" si="0">C3-$C$2</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4">
+        <v>1458291</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5">
+        <v>1458292</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6">
+        <v>1458371</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7">
+        <v>1458375</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8">
+        <v>1458487</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>278</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9">
+        <v>1458706</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>497</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10">
+        <v>1458738</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>529</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11">
+        <v>1460892</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12">
+        <v>1460894</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>2685</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13">
+        <v>1483227</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>25018</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14">
+        <v>1483228</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>25019</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:C14">
+    <sortCondition ref="C2:C14"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1926305E-7F56-884B-A433-D50EECD156B9}">
+  <dimension ref="A1:R31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K3" t="s">
+        <v>75</v>
+      </c>
+      <c r="L3" s="9">
+        <v>1</v>
+      </c>
+      <c r="M3" s="9">
+        <v>2</v>
+      </c>
+      <c r="N3" s="9">
+        <v>3</v>
+      </c>
+      <c r="O3" s="9">
+        <v>4</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>56</v>
+      </c>
+      <c r="K4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4" s="9">
+        <v>1</v>
+      </c>
+      <c r="N4" s="9">
+        <v>2</v>
+      </c>
+      <c r="O4" s="9">
+        <v>3</v>
+      </c>
+      <c r="P4" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="R4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>57</v>
+      </c>
+      <c r="K5" t="s">
+        <v>80</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="9">
+        <v>1</v>
+      </c>
+      <c r="N5" s="9">
+        <v>2</v>
+      </c>
+      <c r="O5" s="9">
+        <v>3</v>
+      </c>
+      <c r="P5" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="R5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>58</v>
+      </c>
+      <c r="K6" t="s">
+        <v>87</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6" t="s">
+        <v>81</v>
+      </c>
+      <c r="N6" t="s">
+        <v>82</v>
+      </c>
+      <c r="O6" t="s">
+        <v>83</v>
+      </c>
+      <c r="P6" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K7" t="s">
+        <v>88</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>2</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q7" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="R7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/modelling/model_manual_drops.xlsx
+++ b/modelling/model_manual_drops.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susanacunha/Documents/PhD/iNat_analysis_clean/modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{314B532D-6303-1F4A-A17C-B43EFBFD479E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF78550E-23AA-B74F-BFFB-B8BB8BA23C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="14280" activeTab="3" xr2:uid="{7C728923-D501-ED44-A77E-3B510BEF037C}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{7C728923-D501-ED44-A77E-3B510BEF037C}"/>
   </bookViews>
   <sheets>
     <sheet name="drops" sheetId="2" r:id="rId1"/>
     <sheet name="table manual drops" sheetId="5" r:id="rId2"/>
     <sheet name="table drop1s" sheetId="6" r:id="rId3"/>
-    <sheet name="table var bins" sheetId="8" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="54">
   <si>
     <t>AIC</t>
   </si>
@@ -201,126 +200,6 @@
   </si>
   <si>
     <t>Y + NPh + PPr + PO + NT + PN + NE:PO + NE:PN + (1|M) + (1|S) + (1|G)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                    labels=c("1","2","3","4","5-10", "&gt;10")),</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                projects_binned = cut(n_projects, breaks = c(-Inf, 0,1,2,3,4,10,Inf), </t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                      labels=c("0","1","2","3","4","5-10", "&gt;10")),</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                obsf_binned = cut(n_obs_fields, breaks = c(-Inf, 0,1,2,3,4,10,Inf), </t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                  labels=c("0","1","2","3","4","5-10", "&gt;10")),</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                notes_binned = cut(length_notes, breaks = c(-Inf, 0, 25, 50,100, 300, Inf), </t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                   labels=c("0", "1-25", "26-50", "51-100", "101-300", "&gt;300")),</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                tags_binned = cut(n_tags, breaks = c(-Inf,0,1,2,5,10,30,Inf), </t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                  labels=c("0","1","2","3-5","6-10","11-30", "&gt;30")),</t>
-  </si>
-  <si>
-    <t># quantile(df %&gt;% filter(length_notes&gt;0) %&gt;% pull(length_notes), c(0.5,0.75, 0.9, 0.95, 0.99,1))</t>
-  </si>
-  <si>
-    <t># ecdf(df %&gt;% filter(length_notes&gt;0) %&gt;% pull(length_notes)) (c(25, 50,100, 300, Inf))</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># # </t>
-  </si>
-  <si>
-    <t># quantile(df %&gt;% filter(n_tags&gt;1) %&gt;% pull(n_tags), c(0.5,0.75, 0.9, 0.95, 0.99,1))</t>
-  </si>
-  <si>
-    <t># ecdf(df %&gt;% filter(n_tags&gt;1) %&gt;% pull(n_tags)) (c(1,2,5,10,30,Inf))</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># </t>
-  </si>
-  <si>
-    <t># quantile(df %&gt;% filter(n_obs_fields&gt;1) %&gt;% pull(n_obs_fields), c(0.5,0.75, 0.9, 0.95, 0.99,1))</t>
-  </si>
-  <si>
-    <t># ecdf(df %&gt;% filter(n_obs_fields&gt;1) %&gt;% pull(n_obs_fields)) (c(1,2,3,4,10,Inf))</t>
-  </si>
-  <si>
-    <t># quantile(df %&gt;% filter(n_projects&gt;1) %&gt;% pull(n_projects), c(0.5,0.75, 0.9, 0.95, 0.99,1))</t>
-  </si>
-  <si>
-    <t># ecdf(df %&gt;% filter(n_projects&gt;1) %&gt;% pull(n_projects)) (c(1,2,3,4,10,Inf))</t>
-  </si>
-  <si>
-    <t># quantile(df %&gt;% pull(n_photos), c(0,0.5,0.75, 0.9, 0.95, 0.99,1))</t>
-  </si>
-  <si>
-    <t># ecdf(df %&gt;% pull(n_photos)) (c(1,2,3,4,10,Inf))</t>
-  </si>
-  <si>
-    <t>photos</t>
-  </si>
-  <si>
-    <t>photos_binned = cut(n_photos, breaks = c(0,1,2,3,4,10,Inf)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "&gt;10"</t>
-  </si>
-  <si>
-    <t>"5-10"</t>
-  </si>
-  <si>
-    <t>projects</t>
-  </si>
-  <si>
-    <t>obsf</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "1-25"</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "26-50"</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "51-100"</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "101-300"</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "&gt;300"</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "&gt;10</t>
-  </si>
-  <si>
-    <t>notes</t>
-  </si>
-  <si>
-    <t>tags</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "&gt;30"</t>
-  </si>
-  <si>
-    <t>"3-5"</t>
-  </si>
-  <si>
-    <t>"6-10"</t>
-  </si>
-  <si>
-    <t>"11-30"</t>
-  </si>
-  <si>
-    <t>TABLE:</t>
   </si>
 </sst>
 </file>
@@ -380,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -391,9 +270,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1645,251 +1521,4 @@
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1926305E-7F56-884B-A433-D50EECD156B9}">
-  <dimension ref="A1:R31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>54</v>
-      </c>
-      <c r="J2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K3" t="s">
-        <v>75</v>
-      </c>
-      <c r="L3" s="9">
-        <v>1</v>
-      </c>
-      <c r="M3" s="9">
-        <v>2</v>
-      </c>
-      <c r="N3" s="9">
-        <v>3</v>
-      </c>
-      <c r="O3" s="9">
-        <v>4</v>
-      </c>
-      <c r="P3" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>56</v>
-      </c>
-      <c r="K4" t="s">
-        <v>79</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4" s="9">
-        <v>1</v>
-      </c>
-      <c r="N4" s="9">
-        <v>2</v>
-      </c>
-      <c r="O4" s="9">
-        <v>3</v>
-      </c>
-      <c r="P4" s="9">
-        <v>4</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="R4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>57</v>
-      </c>
-      <c r="K5" t="s">
-        <v>80</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="9">
-        <v>1</v>
-      </c>
-      <c r="N5" s="9">
-        <v>2</v>
-      </c>
-      <c r="O5" s="9">
-        <v>3</v>
-      </c>
-      <c r="P5" s="9">
-        <v>4</v>
-      </c>
-      <c r="Q5" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="R5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>58</v>
-      </c>
-      <c r="K6" t="s">
-        <v>87</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6" t="s">
-        <v>81</v>
-      </c>
-      <c r="N6" t="s">
-        <v>82</v>
-      </c>
-      <c r="O6" t="s">
-        <v>83</v>
-      </c>
-      <c r="P6" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>59</v>
-      </c>
-      <c r="K7" t="s">
-        <v>88</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-      <c r="N7">
-        <v>2</v>
-      </c>
-      <c r="O7" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="P7" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q7" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="R7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>74</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>